--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10139-2022 artfynd.xlsx
+++ b/artfynd/A 10139-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136578262</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
